--- a/output/pdf_financials_xlsx/IDK.xlsx
+++ b/output/pdf_financials_xlsx/IDK.xlsx
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>0.875701</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.875102</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.87516</v>
       </c>
     </row>
     <row r="92">
@@ -3322,7 +3322,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>0.875701</v>
       </c>

--- a/output/pdf_financials_xlsx/IDK.xlsx
+++ b/output/pdf_financials_xlsx/IDK.xlsx
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.004555</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.482146</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.005286</v>
       </c>
     </row>
     <row r="35">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.004555</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.482146</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.005286</v>
       </c>
     </row>
     <row r="37">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
